--- a/artfynd/A 24187-2026 artfynd.xlsx
+++ b/artfynd/A 24187-2026 artfynd.xlsx
@@ -1390,7 +1390,7 @@
         <v>133582870</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24187-2026 artfynd.xlsx
+++ b/artfynd/A 24187-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105050541</v>
+        <v>67327426</v>
       </c>
       <c r="B2" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ånge, Hls</t>
+          <t>Nordost Rödtjärnen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530436.7531976135</v>
+        <v>530535</v>
       </c>
       <c r="R2" t="n">
-        <v>6911703.079744648</v>
+        <v>6911791</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Calluna AB, JMN0095. Naturvärdesinventering.</t>
+          <t>2017-08-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,37 +756,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Julia Björk</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>JMN0095 Ånge NVI 2022</t>
-        </is>
-      </c>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105050605</v>
+        <v>105050489</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +786,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530501.9649304185</v>
+        <v>530493</v>
       </c>
       <c r="R3" t="n">
-        <v>6911594.006602176</v>
+        <v>6911787</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +843,9 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,15 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105050489</v>
+        <v>105050433</v>
       </c>
       <c r="B4" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +892,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530493.6954841316</v>
+        <v>530554</v>
       </c>
       <c r="R4" t="n">
-        <v>6911786.774018076</v>
+        <v>6911706</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -990,19 +949,9 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1038,37 +987,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105050437</v>
+        <v>105050605</v>
       </c>
       <c r="B5" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530521.6525193041</v>
+        <v>530502</v>
       </c>
       <c r="R5" t="n">
-        <v>6911629.502461188</v>
+        <v>6911594</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1111,19 +1055,9 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1159,53 +1093,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105050523</v>
+        <v>114927666</v>
       </c>
       <c r="B6" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ånge, Hls</t>
+          <t>tovåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530491.334190554</v>
+        <v>530484</v>
       </c>
       <c r="R6" t="n">
-        <v>6911586.010039204</v>
+        <v>6911898</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,27 +1158,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Calluna AB, JMN0095. Naturvärdesinventering.</t>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,31 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Alfred Olofsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Österman</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>JMN0095 Ånge NVI 2022</t>
-        </is>
-      </c>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114927666</v>
+        <v>133582870</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,37 +1206,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>tovåsen, Hls</t>
+          <t>Nylandet, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530484</v>
+        <v>530444</v>
       </c>
       <c r="R7" t="n">
-        <v>6911898</v>
+        <v>6911518</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1350,17 +1264,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,64 +1289,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133582870</v>
+        <v>105050523</v>
       </c>
       <c r="B8" t="n">
-        <v>79123</v>
+        <v>97989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nylandet, Hls</t>
+          <t>Ånge, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530444</v>
+        <v>530491</v>
       </c>
       <c r="R8" t="n">
-        <v>6911518</v>
+        <v>6911586</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,17 +1366,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Calluna AB, JMN0095. Naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,15 +1391,231 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Per Österman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>JMN0095 Ånge NVI 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>105050541</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ånge, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>530436</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6911703</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Calluna AB, JMN0095. Naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Julia Björk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>JMN0095 Ånge NVI 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>105050437</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ånge, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>530521</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6911629</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Calluna AB, JMN0095. Naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Österman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>JMN0095 Ånge NVI 2022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24187-2026 artfynd.xlsx
+++ b/artfynd/A 24187-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67327426</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
           <t>JMN0095 Ånge NVI 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105050489</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
           <t>JMN0095 Ånge NVI 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105050433</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
           <t>JMN0095 Ånge NVI 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105050605</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114927666</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582870</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
           <t>JMN0095 Ånge NVI 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105050523</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
           <t>JMN0095 Ånge NVI 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105050541</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,8 +1661,24 @@
           <t>JMN0095 Ånge NVI 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105050437</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>